--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/58.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/58.xlsx
@@ -426,13 +426,13 @@
         <v>-7.019021277172783</v>
       </c>
       <c r="E2">
-        <v>-21.42829276207697</v>
+        <v>-24.44663390003946</v>
       </c>
       <c r="F2">
-        <v>-4.550233059601428</v>
+        <v>-4.613531097951547</v>
       </c>
       <c r="G2">
-        <v>-11.28232710632238</v>
+        <v>-12.44675853103239</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.026833246041703</v>
       </c>
       <c r="E3">
-        <v>-19.86716474656873</v>
+        <v>-26.09748004258767</v>
       </c>
       <c r="F3">
-        <v>-4.341802567178628</v>
+        <v>-4.26979341722067</v>
       </c>
       <c r="G3">
-        <v>-10.7533317240567</v>
+        <v>-12.48241641703588</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.992139826520342</v>
       </c>
       <c r="E4">
-        <v>-23.37892388393297</v>
+        <v>-25.76721390473427</v>
       </c>
       <c r="F4">
-        <v>-4.522569730184939</v>
+        <v>-3.676716319879739</v>
       </c>
       <c r="G4">
-        <v>-11.85919628763147</v>
+        <v>-12.50397137904208</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.914203878657199</v>
       </c>
       <c r="E5">
-        <v>-22.4800217934104</v>
+        <v>-26.15410408157958</v>
       </c>
       <c r="F5">
-        <v>-4.028586911771302</v>
+        <v>-4.444373504095471</v>
       </c>
       <c r="G5">
-        <v>-11.82742167154554</v>
+        <v>-12.84987372971283</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.798186275521757</v>
       </c>
       <c r="E6">
-        <v>-21.67094651330398</v>
+        <v>-24.18794482235129</v>
       </c>
       <c r="F6">
-        <v>-4.887072096601791</v>
+        <v>-4.288880658915976</v>
       </c>
       <c r="G6">
-        <v>-9.559661561143844</v>
+        <v>-13.40105307763717</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.648857128537172</v>
       </c>
       <c r="E7">
-        <v>-22.25522834366964</v>
+        <v>-25.05214974502709</v>
       </c>
       <c r="F7">
-        <v>-4.464640340972364</v>
+        <v>-3.774114102366099</v>
       </c>
       <c r="G7">
-        <v>-10.75186184183726</v>
+        <v>-14.86874537119935</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.470206964331818</v>
       </c>
       <c r="E8">
-        <v>-22.37701259515792</v>
+        <v>-24.16202836560539</v>
       </c>
       <c r="F8">
-        <v>-3.799984016355527</v>
+        <v>-4.078060326536099</v>
       </c>
       <c r="G8">
-        <v>-11.17303937697996</v>
+        <v>-13.53304618356068</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.267705482181476</v>
       </c>
       <c r="E9">
-        <v>-24.42896379446153</v>
+        <v>-27.61950015656568</v>
       </c>
       <c r="F9">
-        <v>-3.720051532189792</v>
+        <v>-3.052481011049907</v>
       </c>
       <c r="G9">
-        <v>-11.41539779481893</v>
+        <v>-11.60288060979893</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.048942630425649</v>
       </c>
       <c r="E10">
-        <v>-22.87982717812559</v>
+        <v>-25.39981880849197</v>
       </c>
       <c r="F10">
-        <v>-3.935926562461551</v>
+        <v>-4.020486306939325</v>
       </c>
       <c r="G10">
-        <v>-11.71435329919727</v>
+        <v>-12.80769075845144</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.820937938530038</v>
       </c>
       <c r="E11">
-        <v>-23.64652046999422</v>
+        <v>-26.31807106844931</v>
       </c>
       <c r="F11">
-        <v>-3.744377369340402</v>
+        <v>-3.813242036637333</v>
       </c>
       <c r="G11">
-        <v>-10.46613858797939</v>
+        <v>-11.99288273759831</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.590665949560323</v>
       </c>
       <c r="E12">
-        <v>-23.72252184926495</v>
+        <v>-26.96478244148472</v>
       </c>
       <c r="F12">
-        <v>-3.741285902193154</v>
+        <v>-2.987799599137113</v>
       </c>
       <c r="G12">
-        <v>-10.59164799046424</v>
+        <v>-12.1662692496721</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.362175371651267</v>
       </c>
       <c r="E13">
-        <v>-24.60194697308053</v>
+        <v>-28.01655675755822</v>
       </c>
       <c r="F13">
-        <v>-3.098471969253335</v>
+        <v>-2.599431967845607</v>
       </c>
       <c r="G13">
-        <v>-10.8530751506094</v>
+        <v>-11.73320354549788</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.144446450533784</v>
       </c>
       <c r="E14">
-        <v>-22.35179352340921</v>
+        <v>-26.68695150416612</v>
       </c>
       <c r="F14">
-        <v>-2.846195161832954</v>
+        <v>-2.668816849871496</v>
       </c>
       <c r="G14">
-        <v>-8.399209412172038</v>
+        <v>-11.96055857095287</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.942631411275419</v>
       </c>
       <c r="E15">
-        <v>-24.42432210860367</v>
+        <v>-27.97630768057804</v>
       </c>
       <c r="F15">
-        <v>-3.427098571822344</v>
+        <v>-3.30622899897766</v>
       </c>
       <c r="G15">
-        <v>-9.773330791339486</v>
+        <v>-11.76917924387314</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.760138084050496</v>
       </c>
       <c r="E16">
-        <v>-25.52084680482097</v>
+        <v>-28.90714909827671</v>
       </c>
       <c r="F16">
-        <v>-2.959750250510919</v>
+        <v>-2.232797383733948</v>
       </c>
       <c r="G16">
-        <v>-10.73139604931349</v>
+        <v>-11.32595678598444</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.601533488089103</v>
       </c>
       <c r="E17">
-        <v>-27.53689626219176</v>
+        <v>-30.74719714910239</v>
       </c>
       <c r="F17">
-        <v>-3.144650138489796</v>
+        <v>-2.507272780814551</v>
       </c>
       <c r="G17">
-        <v>-9.01509668320697</v>
+        <v>-11.65301882199119</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.471250648102623</v>
       </c>
       <c r="E18">
-        <v>-25.71625951519996</v>
+        <v>-30.85930631587328</v>
       </c>
       <c r="F18">
-        <v>-3.649691661730808</v>
+        <v>-2.698481514933149</v>
       </c>
       <c r="G18">
-        <v>-8.912502876944956</v>
+        <v>-10.84659641298905</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.373107870649613</v>
       </c>
       <c r="E19">
-        <v>-27.30943101278648</v>
+        <v>-28.56915738376621</v>
       </c>
       <c r="F19">
-        <v>-2.767107612418074</v>
+        <v>-2.194034759487348</v>
       </c>
       <c r="G19">
-        <v>-8.711407098707468</v>
+        <v>-10.18927104343906</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.310360756359507</v>
       </c>
       <c r="E20">
-        <v>-28.24341066297246</v>
+        <v>-27.3270920614164</v>
       </c>
       <c r="F20">
-        <v>-3.04393640129003</v>
+        <v>-2.600693571400071</v>
       </c>
       <c r="G20">
-        <v>-8.340278391027471</v>
+        <v>-11.20966394228092</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.285674450438912</v>
       </c>
       <c r="E21">
-        <v>-26.88567000057071</v>
+        <v>-31.19849807599581</v>
       </c>
       <c r="F21">
-        <v>-2.620975318890213</v>
+        <v>-2.185878654039384</v>
       </c>
       <c r="G21">
-        <v>-8.878033476790065</v>
+        <v>-10.48698178269464</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.304067302878337</v>
       </c>
       <c r="E22">
-        <v>-26.40130442071029</v>
+        <v>-29.13276220181285</v>
       </c>
       <c r="F22">
-        <v>-2.335868654562082</v>
+        <v>-1.743301831541276</v>
       </c>
       <c r="G22">
-        <v>-8.057998104530435</v>
+        <v>-10.69686705933889</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.367390177241445</v>
       </c>
       <c r="E23">
-        <v>-27.00748595137705</v>
+        <v>-31.36996648005924</v>
       </c>
       <c r="F23">
-        <v>-2.418543863198487</v>
+        <v>-2.591128412999944</v>
       </c>
       <c r="G23">
-        <v>-7.940626022981114</v>
+        <v>-9.853234118475335</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.473671606269372</v>
       </c>
       <c r="E24">
-        <v>-28.08323853732116</v>
+        <v>-30.54821147273135</v>
       </c>
       <c r="F24">
-        <v>-1.889558380179556</v>
+        <v>-1.946600587903733</v>
       </c>
       <c r="G24">
-        <v>-8.537295577160577</v>
+        <v>-9.502548029500339</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.62379553715961</v>
       </c>
       <c r="E25">
-        <v>-26.62488423941699</v>
+        <v>-30.24806421550296</v>
       </c>
       <c r="F25">
-        <v>-2.530877109957323</v>
+        <v>-2.600380448521812</v>
       </c>
       <c r="G25">
-        <v>-8.412789269974128</v>
+        <v>-10.4581899681396</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.81552699291978</v>
       </c>
       <c r="E26">
-        <v>-27.02867015278493</v>
+        <v>-28.81630790968284</v>
       </c>
       <c r="F26">
-        <v>-2.091204543573429</v>
+        <v>-2.621981785284615</v>
       </c>
       <c r="G26">
-        <v>-8.04221342339919</v>
+        <v>-11.11607481988572</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.0445771303175</v>
       </c>
       <c r="E27">
-        <v>-26.17463618273036</v>
+        <v>-29.4234947615793</v>
       </c>
       <c r="F27">
-        <v>-2.743698777982363</v>
+        <v>-2.727844654260184</v>
       </c>
       <c r="G27">
-        <v>-8.330048805311122</v>
+        <v>-10.44924156354694</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.303873918553606</v>
       </c>
       <c r="E28">
-        <v>-27.08776221011102</v>
+        <v>-29.10629327123802</v>
       </c>
       <c r="F28">
-        <v>-2.886809187224811</v>
+        <v>-2.562036149813626</v>
       </c>
       <c r="G28">
-        <v>-8.017496890402992</v>
+        <v>-10.00797232752641</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.58576102890872</v>
       </c>
       <c r="E29">
-        <v>-26.13658794411791</v>
+        <v>-28.58155634559922</v>
       </c>
       <c r="F29">
-        <v>-2.289608476952744</v>
+        <v>-1.769574332088465</v>
       </c>
       <c r="G29">
-        <v>-9.029229402114119</v>
+        <v>-11.845964037111</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.881857178938573</v>
       </c>
       <c r="E30">
-        <v>-25.59411298579107</v>
+        <v>-30.59070214434532</v>
       </c>
       <c r="F30">
-        <v>-2.327272686023232</v>
+        <v>-2.12325656348995</v>
       </c>
       <c r="G30">
-        <v>-8.969874631140526</v>
+        <v>-11.25246267501262</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.181751827780626</v>
       </c>
       <c r="E31">
-        <v>-25.19283131854937</v>
+        <v>-28.59241562626961</v>
       </c>
       <c r="F31">
-        <v>-2.228799682648038</v>
+        <v>-2.070013248675012</v>
       </c>
       <c r="G31">
-        <v>-9.111916898048495</v>
+        <v>-12.41697355281557</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.472755205660703</v>
       </c>
       <c r="E32">
-        <v>-24.29451340117379</v>
+        <v>-29.77214197542984</v>
       </c>
       <c r="F32">
-        <v>-2.512724266692374</v>
+        <v>-2.632420042927291</v>
       </c>
       <c r="G32">
-        <v>-9.881108911915998</v>
+        <v>-11.56019112507003</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.747497736574678</v>
       </c>
       <c r="E33">
-        <v>-25.61380731925042</v>
+        <v>-29.0486639110164</v>
       </c>
       <c r="F33">
-        <v>-1.882924814017938</v>
+        <v>-2.448285566428601</v>
       </c>
       <c r="G33">
-        <v>-9.31844197097039</v>
+        <v>-10.11769704888001</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.997507817619154</v>
       </c>
       <c r="E34">
-        <v>-24.95405394107293</v>
+        <v>-26.9968938506731</v>
       </c>
       <c r="F34">
-        <v>-2.206195192960445</v>
+        <v>-2.986400486593785</v>
       </c>
       <c r="G34">
-        <v>-9.866449816268107</v>
+        <v>-11.04368312057848</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.215453837256936</v>
       </c>
       <c r="E35">
-        <v>-22.16444149676387</v>
+        <v>-26.67885912111442</v>
       </c>
       <c r="F35">
-        <v>-2.382176877480783</v>
+        <v>-3.008755637693135</v>
       </c>
       <c r="G35">
-        <v>-10.46019946928193</v>
+        <v>-11.34556845775908</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.39457333348286</v>
       </c>
       <c r="E36">
-        <v>-24.25295559520541</v>
+        <v>-27.12591007515163</v>
       </c>
       <c r="F36">
-        <v>-2.380511859001156</v>
+        <v>-2.09768817523514</v>
       </c>
       <c r="G36">
-        <v>-10.41212372696064</v>
+        <v>-12.29364248929556</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.531886797262078</v>
       </c>
       <c r="E37">
-        <v>-23.57511549184128</v>
+        <v>-26.31161799298838</v>
       </c>
       <c r="F37">
-        <v>-2.058414448301013</v>
+        <v>-2.336822105442705</v>
       </c>
       <c r="G37">
-        <v>-10.04030642580847</v>
+        <v>-11.57962733793109</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.625784462409542</v>
       </c>
       <c r="E38">
-        <v>-23.53649666550386</v>
+        <v>-26.84548885070065</v>
       </c>
       <c r="F38">
-        <v>-2.12132729580883</v>
+        <v>-2.289479251637907</v>
       </c>
       <c r="G38">
-        <v>-9.803258123014498</v>
+        <v>-12.01407022904965</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.675143252456809</v>
       </c>
       <c r="E39">
-        <v>-21.79100994466935</v>
+        <v>-25.2106191644515</v>
       </c>
       <c r="F39">
-        <v>-2.413813885328502</v>
+        <v>-1.547540390176891</v>
       </c>
       <c r="G39">
-        <v>-10.5906250318926</v>
+        <v>-11.53078354904468</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.680943184193032</v>
       </c>
       <c r="E40">
-        <v>-22.75370012006396</v>
+        <v>-25.88875361862613</v>
       </c>
       <c r="F40">
-        <v>-2.179342835231296</v>
+        <v>-2.041828876162162</v>
       </c>
       <c r="G40">
-        <v>-10.28601842627872</v>
+        <v>-12.12104057651458</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.649178435709556</v>
       </c>
       <c r="E41">
-        <v>-21.15916102332712</v>
+        <v>-24.3360802640902</v>
       </c>
       <c r="F41">
-        <v>-1.991088887638483</v>
+        <v>-2.64808447051423</v>
       </c>
       <c r="G41">
-        <v>-9.095658808905135</v>
+        <v>-12.7948657050323</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.586245922264567</v>
       </c>
       <c r="E42">
-        <v>-22.98596102344336</v>
+        <v>-25.47057168638781</v>
       </c>
       <c r="F42">
-        <v>-1.388982585607038</v>
+        <v>-2.866904346902942</v>
       </c>
       <c r="G42">
-        <v>-9.969977196372195</v>
+        <v>-9.987966700832594</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.500565203952489</v>
       </c>
       <c r="E43">
-        <v>-21.83539351841852</v>
+        <v>-26.23457959316989</v>
       </c>
       <c r="F43">
-        <v>-2.046091654816968</v>
+        <v>-1.973112486630331</v>
       </c>
       <c r="G43">
-        <v>-10.16062489288774</v>
+        <v>-9.624399279164294</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.399630271634328</v>
       </c>
       <c r="E44">
-        <v>-22.29024703317096</v>
+        <v>-23.67276297686867</v>
       </c>
       <c r="F44">
-        <v>-2.182804582607595</v>
+        <v>-3.093278105637782</v>
       </c>
       <c r="G44">
-        <v>-8.674050902842332</v>
+        <v>-11.15405339831224</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.296614891460058</v>
       </c>
       <c r="E45">
-        <v>-19.9384066996574</v>
+        <v>-22.53793191902049</v>
       </c>
       <c r="F45">
-        <v>-2.458096749947358</v>
+        <v>-1.970325858687314</v>
       </c>
       <c r="G45">
-        <v>-9.455637599208867</v>
+        <v>-11.17585996177942</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.202435116440673</v>
       </c>
       <c r="E46">
-        <v>-20.31774791033193</v>
+        <v>-25.90028764192367</v>
       </c>
       <c r="F46">
-        <v>-1.964500779110828</v>
+        <v>-2.253552957378493</v>
       </c>
       <c r="G46">
-        <v>-9.97540318051106</v>
+        <v>-12.11955083102191</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.124950044413203</v>
       </c>
       <c r="E47">
-        <v>-18.64704440926008</v>
+        <v>-24.33006645060802</v>
       </c>
       <c r="F47">
-        <v>-2.168212890807282</v>
+        <v>-1.527556854951756</v>
       </c>
       <c r="G47">
-        <v>-8.502332905720335</v>
+        <v>-10.64343816488059</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.073035907494694</v>
       </c>
       <c r="E48">
-        <v>-19.77799456488369</v>
+        <v>-23.31440671474569</v>
       </c>
       <c r="F48">
-        <v>-1.909604042959902</v>
+        <v>-2.138052033671352</v>
       </c>
       <c r="G48">
-        <v>-7.29567216211138</v>
+        <v>-11.66721113071805</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.054956087765963</v>
       </c>
       <c r="E49">
-        <v>-18.47763419663313</v>
+        <v>-22.84622137251467</v>
       </c>
       <c r="F49">
-        <v>-2.845191180540761</v>
+        <v>-2.357390468054216</v>
       </c>
       <c r="G49">
-        <v>-9.265330888883861</v>
+        <v>-11.32216621134197</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.076024792464274</v>
       </c>
       <c r="E50">
-        <v>-19.12770569738223</v>
+        <v>-23.03880831511287</v>
       </c>
       <c r="F50">
-        <v>-2.714009261898626</v>
+        <v>-2.341230676760404</v>
       </c>
       <c r="G50">
-        <v>-9.222141511778529</v>
+        <v>-9.774784120831226</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.138760697626373</v>
       </c>
       <c r="E51">
-        <v>-16.76837979633398</v>
+        <v>-23.397834791389</v>
       </c>
       <c r="F51">
-        <v>-2.885052219963474</v>
+        <v>-2.137543416086033</v>
       </c>
       <c r="G51">
-        <v>-7.494698849386825</v>
+        <v>-11.18629149077366</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.241936940278651</v>
       </c>
       <c r="E52">
-        <v>-18.77061287950738</v>
+        <v>-22.64531109469037</v>
       </c>
       <c r="F52">
-        <v>-2.835575491729065</v>
+        <v>-2.510054438553151</v>
       </c>
       <c r="G52">
-        <v>-9.430490695292562</v>
+        <v>-11.1195542032475</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.386130954849548</v>
       </c>
       <c r="E53">
-        <v>-18.28688128600803</v>
+        <v>-22.42032744904129</v>
       </c>
       <c r="F53">
-        <v>-3.352952233965163</v>
+        <v>-2.662371323110313</v>
       </c>
       <c r="G53">
-        <v>-9.934759612925427</v>
+        <v>-11.99965611377166</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.566574388662767</v>
       </c>
       <c r="E54">
-        <v>-17.44623801359414</v>
+        <v>-22.06506413466554</v>
       </c>
       <c r="F54">
-        <v>-2.97490937398215</v>
+        <v>-1.493796741450662</v>
       </c>
       <c r="G54">
-        <v>-8.795869047050893</v>
+        <v>-10.59232003120871</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.773008314470372</v>
       </c>
       <c r="E55">
-        <v>-18.01684838093065</v>
+        <v>-24.07912106347296</v>
       </c>
       <c r="F55">
-        <v>-2.696186937227395</v>
+        <v>-1.976449978896211</v>
       </c>
       <c r="G55">
-        <v>-9.591922827424042</v>
+        <v>-11.30171035045482</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.998917891748725</v>
       </c>
       <c r="E56">
-        <v>-17.41800297815632</v>
+        <v>-21.61678143569824</v>
       </c>
       <c r="F56">
-        <v>-3.50734169376413</v>
+        <v>-1.816840976092205</v>
       </c>
       <c r="G56">
-        <v>-9.616407622232492</v>
+        <v>-11.77794556846113</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.235592843205374</v>
       </c>
       <c r="E57">
-        <v>-16.88483403391524</v>
+        <v>-21.17921763470709</v>
       </c>
       <c r="F57">
-        <v>-3.196661670976772</v>
+        <v>-2.509876339561549</v>
       </c>
       <c r="G57">
-        <v>-9.612146950123451</v>
+        <v>-10.96198547776035</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.47314995791789</v>
       </c>
       <c r="E58">
-        <v>-17.93590643651755</v>
+        <v>-20.34549387057692</v>
       </c>
       <c r="F58">
-        <v>-3.086709152133583</v>
+        <v>-1.835871888804121</v>
       </c>
       <c r="G58">
-        <v>-10.50929154908379</v>
+        <v>-10.89293742944777</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.700785674831675</v>
       </c>
       <c r="E59">
-        <v>-17.25908071133114</v>
+        <v>-21.19046183566813</v>
       </c>
       <c r="F59">
-        <v>-3.315331099999621</v>
+        <v>-2.508383621501705</v>
       </c>
       <c r="G59">
-        <v>-7.974592220214037</v>
+        <v>-11.02287303131862</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.909048232749944</v>
       </c>
       <c r="E60">
-        <v>-16.21568407217183</v>
+        <v>-21.60852149910825</v>
       </c>
       <c r="F60">
-        <v>-3.067506767369287</v>
+        <v>-2.215187121117834</v>
       </c>
       <c r="G60">
-        <v>-7.77589327694698</v>
+        <v>-11.79633233838624</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.091382547089468</v>
       </c>
       <c r="E61">
-        <v>-18.13636386694109</v>
+        <v>-21.00315056528887</v>
       </c>
       <c r="F61">
-        <v>-3.392346902540099</v>
+        <v>-2.835648388060511</v>
       </c>
       <c r="G61">
-        <v>-10.09802247674012</v>
+        <v>-11.36411744441562</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.241105329560607</v>
       </c>
       <c r="E62">
-        <v>-18.18606386917527</v>
+        <v>-20.86702463661829</v>
       </c>
       <c r="F62">
-        <v>-3.45639709849196</v>
+        <v>-2.83579583745821</v>
       </c>
       <c r="G62">
-        <v>-9.752325379892811</v>
+        <v>-11.36197883199725</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.350728763676647</v>
       </c>
       <c r="E63">
-        <v>-17.68180017452514</v>
+        <v>-22.21193160368231</v>
       </c>
       <c r="F63">
-        <v>-3.350231047046967</v>
+        <v>-2.774830481714374</v>
       </c>
       <c r="G63">
-        <v>-9.295744870753147</v>
+        <v>-11.0743619460909</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.421693381429805</v>
       </c>
       <c r="E64">
-        <v>-18.32494763851651</v>
+        <v>-21.12299210142785</v>
       </c>
       <c r="F64">
-        <v>-3.073310309393301</v>
+        <v>-2.906942656949853</v>
       </c>
       <c r="G64">
-        <v>-8.905239540031795</v>
+        <v>-11.13235608284786</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.455287646878752</v>
       </c>
       <c r="E65">
-        <v>-17.87310103050517</v>
+        <v>-20.82775823849779</v>
       </c>
       <c r="F65">
-        <v>-3.593036301583738</v>
+        <v>-3.140820595986654</v>
       </c>
       <c r="G65">
-        <v>-9.665380522394932</v>
+        <v>-11.22525330122535</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.454742134073649</v>
       </c>
       <c r="E66">
-        <v>-17.8254750693665</v>
+        <v>-21.83633544101212</v>
       </c>
       <c r="F66">
-        <v>-3.27883488896708</v>
+        <v>-2.783907731714251</v>
       </c>
       <c r="G66">
-        <v>-9.257451790500397</v>
+        <v>-11.17381735518169</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.423226762476913</v>
       </c>
       <c r="E67">
-        <v>-17.47176502157538</v>
+        <v>-23.62645480166623</v>
       </c>
       <c r="F67">
-        <v>-3.618175595523898</v>
+        <v>-2.998612278845855</v>
       </c>
       <c r="G67">
-        <v>-9.676626445591836</v>
+        <v>-12.0039498913361</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.367788940376542</v>
       </c>
       <c r="E68">
-        <v>-17.46725918993775</v>
+        <v>-21.55607271315141</v>
       </c>
       <c r="F68">
-        <v>-3.071687537651216</v>
+        <v>-2.617935210521939</v>
       </c>
       <c r="G68">
-        <v>-7.85211527744316</v>
+        <v>-11.81613602180217</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.295896077294008</v>
       </c>
       <c r="E69">
-        <v>-18.04012926580408</v>
+        <v>-21.14959688622292</v>
       </c>
       <c r="F69">
-        <v>-3.117125974796978</v>
+        <v>-3.24364087149174</v>
       </c>
       <c r="G69">
-        <v>-9.5677757082606</v>
+        <v>-10.99972900745358</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.212278327360599</v>
       </c>
       <c r="E70">
-        <v>-18.23737600815618</v>
+        <v>-21.33558584219195</v>
       </c>
       <c r="F70">
-        <v>-3.88786634248593</v>
+        <v>-2.598324440628064</v>
       </c>
       <c r="G70">
-        <v>-9.417447145867834</v>
+        <v>-10.46730058946367</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.120134259105695</v>
       </c>
       <c r="E71">
-        <v>-18.35757982221578</v>
+        <v>-22.21637856515784</v>
       </c>
       <c r="F71">
-        <v>-3.976303674776208</v>
+        <v>-3.801160298067503</v>
       </c>
       <c r="G71">
-        <v>-7.228103927654855</v>
+        <v>-11.33789130265351</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.02564626156901</v>
       </c>
       <c r="E72">
-        <v>-16.37781249859444</v>
+        <v>-20.49996464745256</v>
       </c>
       <c r="F72">
-        <v>-3.852101579870061</v>
+        <v>-3.028871711702718</v>
       </c>
       <c r="G72">
-        <v>-9.339960516975653</v>
+        <v>-12.29815145232005</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.931874611249256</v>
       </c>
       <c r="E73">
-        <v>-18.95566444135682</v>
+        <v>-22.52444612342564</v>
       </c>
       <c r="F73">
-        <v>-3.671801616078929</v>
+        <v>-3.495853066254703</v>
       </c>
       <c r="G73">
-        <v>-10.6893057733272</v>
+        <v>-11.00313886935903</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.840656837787161</v>
       </c>
       <c r="E74">
-        <v>-18.92960760191669</v>
+        <v>-22.39696958010973</v>
       </c>
       <c r="F74">
-        <v>-3.564272900256331</v>
+        <v>-2.842682884045084</v>
       </c>
       <c r="G74">
-        <v>-9.657812615292157</v>
+        <v>-11.8663305132686</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.749965415873895</v>
       </c>
       <c r="E75">
-        <v>-19.25939824999929</v>
+        <v>-23.4248743096888</v>
       </c>
       <c r="F75">
-        <v>-3.580715164834498</v>
+        <v>-3.175761133036738</v>
       </c>
       <c r="G75">
-        <v>-9.63476459724775</v>
+        <v>-10.82854069761786</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.662133022421251</v>
       </c>
       <c r="E76">
-        <v>-18.90541649376771</v>
+        <v>-23.78289999320922</v>
       </c>
       <c r="F76">
-        <v>-3.584549677542057</v>
+        <v>-2.810172776954815</v>
       </c>
       <c r="G76">
-        <v>-9.263943770302907</v>
+        <v>-9.241223496266889</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.575852263265062</v>
       </c>
       <c r="E77">
-        <v>-18.55890219117478</v>
+        <v>-22.14029114488096</v>
       </c>
       <c r="F77">
-        <v>-4.289613764067454</v>
+        <v>-3.596532012023552</v>
       </c>
       <c r="G77">
-        <v>-8.997818946037514</v>
+        <v>-10.9972527193902</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.486483063125736</v>
       </c>
       <c r="E78">
-        <v>-20.17760069674254</v>
+        <v>-22.45226677621739</v>
       </c>
       <c r="F78">
-        <v>-4.104387499331873</v>
+        <v>-4.324047340267024</v>
       </c>
       <c r="G78">
-        <v>-8.576929428356733</v>
+        <v>-11.3826200834346</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.390326569684557</v>
       </c>
       <c r="E79">
-        <v>-19.06418932095064</v>
+        <v>-23.08878908273553</v>
       </c>
       <c r="F79">
-        <v>-4.123022452425251</v>
+        <v>-3.661115676582816</v>
       </c>
       <c r="G79">
-        <v>-9.543367055999552</v>
+        <v>-11.10868237169653</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.285415907020919</v>
       </c>
       <c r="E80">
-        <v>-19.3884054175298</v>
+        <v>-24.05218570007534</v>
       </c>
       <c r="F80">
-        <v>-4.820659396817146</v>
+        <v>-3.218359926725702</v>
       </c>
       <c r="G80">
-        <v>-9.631851317173192</v>
+        <v>-11.61203757876056</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.169121979136944</v>
       </c>
       <c r="E81">
-        <v>-21.08062369861209</v>
+        <v>-23.07346472669358</v>
       </c>
       <c r="F81">
-        <v>-3.53921892815866</v>
+        <v>-3.895759855467206</v>
       </c>
       <c r="G81">
-        <v>-9.013133529702182</v>
+        <v>-11.06945240705617</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.03973508101253</v>
       </c>
       <c r="E82">
-        <v>-21.85691735537698</v>
+        <v>-25.95991858765667</v>
       </c>
       <c r="F82">
-        <v>-3.809395926786135</v>
+        <v>-3.818242890648034</v>
       </c>
       <c r="G82">
-        <v>-8.124728770965524</v>
+        <v>-11.01028633717831</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.894846170065058</v>
       </c>
       <c r="E83">
-        <v>-20.15147593019229</v>
+        <v>-25.79528138663381</v>
       </c>
       <c r="F83">
-        <v>-4.203249835386383</v>
+        <v>-3.690074572617283</v>
       </c>
       <c r="G83">
-        <v>-9.177343209541112</v>
+        <v>-11.38554660569132</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.739228039450357</v>
       </c>
       <c r="E84">
-        <v>-21.86927103246991</v>
+        <v>-25.58009283026332</v>
       </c>
       <c r="F84">
-        <v>-4.116809696904254</v>
+        <v>-4.446349988718551</v>
       </c>
       <c r="G84">
-        <v>-10.24318327754609</v>
+        <v>-10.3009291233876</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.575296189852563</v>
       </c>
       <c r="E85">
-        <v>-23.75700617883336</v>
+        <v>-24.44401191358902</v>
       </c>
       <c r="F85">
-        <v>-4.345141716179313</v>
+        <v>-3.672637438788354</v>
       </c>
       <c r="G85">
-        <v>-9.502375881132297</v>
+        <v>-12.13224677316501</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.404279958172587</v>
       </c>
       <c r="E86">
-        <v>-22.33440418321975</v>
+        <v>-28.07956141642693</v>
       </c>
       <c r="F86">
-        <v>-5.053288157810527</v>
+        <v>-4.413565692017955</v>
       </c>
       <c r="G86">
-        <v>-9.876454284887783</v>
+        <v>-9.641163881775162</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.23080645037659</v>
       </c>
       <c r="E87">
-        <v>-23.80940062310211</v>
+        <v>-28.48959209545145</v>
       </c>
       <c r="F87">
-        <v>-4.262090428742037</v>
+        <v>-4.864967112458086</v>
       </c>
       <c r="G87">
-        <v>-8.892662777528104</v>
+        <v>-11.09159664616835</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.059415068409432</v>
       </c>
       <c r="E88">
-        <v>-24.56076050198077</v>
+        <v>-29.27771865479838</v>
       </c>
       <c r="F88">
-        <v>-4.30150497813464</v>
+        <v>-4.183485817522989</v>
       </c>
       <c r="G88">
-        <v>-9.459391757850399</v>
+        <v>-9.894562968987596</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.894129804379981</v>
       </c>
       <c r="E89">
-        <v>-27.18329036930282</v>
+        <v>-27.79145084311093</v>
       </c>
       <c r="F89">
-        <v>-5.444922041771271</v>
+        <v>-4.85953550739793</v>
       </c>
       <c r="G89">
-        <v>-9.618092689911983</v>
+        <v>-10.17390018050022</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.73759386741825</v>
       </c>
       <c r="E90">
-        <v>-28.23569414326339</v>
+        <v>-29.89114800811441</v>
       </c>
       <c r="F90">
-        <v>-4.650550008815254</v>
+        <v>-4.589121595693254</v>
       </c>
       <c r="G90">
-        <v>-10.47290534306166</v>
+        <v>-10.8804301884004</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.592490975861605</v>
       </c>
       <c r="E91">
-        <v>-29.35451704549446</v>
+        <v>-30.60110857761495</v>
       </c>
       <c r="F91">
-        <v>-4.71858465197458</v>
+        <v>-4.326446292265531</v>
       </c>
       <c r="G91">
-        <v>-9.420572300856906</v>
+        <v>-12.05163498928376</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.463947731365417</v>
       </c>
       <c r="E92">
-        <v>-30.32193041927907</v>
+        <v>-32.28111582853555</v>
       </c>
       <c r="F92">
-        <v>-5.324382159152901</v>
+        <v>-4.511293164730629</v>
       </c>
       <c r="G92">
-        <v>-8.144462932925119</v>
+        <v>-11.77777342009309</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.354285130339908</v>
       </c>
       <c r="E93">
-        <v>-30.49133383919501</v>
+        <v>-31.94248107071597</v>
       </c>
       <c r="F93">
-        <v>-5.450963325239888</v>
+        <v>-5.415848831035217</v>
       </c>
       <c r="G93">
-        <v>-9.547309915736824</v>
+        <v>-11.32874757587404</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.262951377065496</v>
       </c>
       <c r="E94">
-        <v>-32.88164355940373</v>
+        <v>-32.25317514390823</v>
       </c>
       <c r="F94">
-        <v>-5.554152224239219</v>
+        <v>-5.096075819267329</v>
       </c>
       <c r="G94">
-        <v>-10.24147834659336</v>
+        <v>-10.83530745270013</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.193989877920407</v>
       </c>
       <c r="E95">
-        <v>-33.84866522018667</v>
+        <v>-36.6161696543903</v>
       </c>
       <c r="F95">
-        <v>-5.97965059599381</v>
+        <v>-5.259352832930931</v>
       </c>
       <c r="G95">
-        <v>-9.88841528592117</v>
+        <v>-10.61075314877137</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.150809134689892</v>
       </c>
       <c r="E96">
-        <v>-34.41908539161486</v>
+        <v>-38.72291765342371</v>
       </c>
       <c r="F96">
-        <v>-5.396996845682305</v>
+        <v>-6.208644480823706</v>
       </c>
       <c r="G96">
-        <v>-10.51131760295382</v>
+        <v>-12.55940646409717</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.134660336117647</v>
       </c>
       <c r="E97">
-        <v>-35.99625099782127</v>
+        <v>-39.04269358123835</v>
       </c>
       <c r="F97">
-        <v>-5.452977914763496</v>
+        <v>-5.554083469744787</v>
       </c>
       <c r="G97">
-        <v>-10.75616224049278</v>
+        <v>-11.40216554429846</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.148915219967118</v>
       </c>
       <c r="E98">
-        <v>-38.38919176142845</v>
+        <v>-41.63815223094256</v>
       </c>
       <c r="F98">
-        <v>-5.602743427720036</v>
+        <v>-5.967317033733528</v>
       </c>
       <c r="G98">
-        <v>-9.60288404370457</v>
+        <v>-11.07684485524536</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.192835901603401</v>
       </c>
       <c r="E99">
-        <v>-41.31249834386597</v>
+        <v>-39.94578903869203</v>
       </c>
       <c r="F99">
-        <v>-5.93692257699001</v>
+        <v>-6.722356111486118</v>
       </c>
       <c r="G99">
-        <v>-9.98657958225164</v>
+        <v>-13.03269860711908</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.274748457640427</v>
       </c>
       <c r="E100">
-        <v>-42.78859520293219</v>
+        <v>-44.41559892983002</v>
       </c>
       <c r="F100">
-        <v>-6.116222701325962</v>
+        <v>-7.478339113894197</v>
       </c>
       <c r="G100">
-        <v>-11.16202188142527</v>
+        <v>-11.29200383093367</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.385660531470185</v>
       </c>
       <c r="E101">
-        <v>-43.19185354907823</v>
+        <v>-46.66730111761196</v>
       </c>
       <c r="F101">
-        <v>-6.149186753752966</v>
+        <v>-7.6282123146131</v>
       </c>
       <c r="G101">
-        <v>-11.25835544607252</v>
+        <v>-13.32249052144472</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.539142302828196</v>
       </c>
       <c r="E102">
-        <v>-45.67580984752857</v>
+        <v>-47.08054701318192</v>
       </c>
       <c r="F102">
-        <v>-6.719067078713302</v>
+        <v>-7.239702618312014</v>
       </c>
       <c r="G102">
-        <v>-12.56798077704389</v>
+        <v>-12.42185329694046</v>
       </c>
     </row>
   </sheetData>
